--- a/Employee Details.xlsx
+++ b/Employee Details.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GOPI\OneDrive\Desktop\EmployeePVC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B861DD-1140-4787-9272-00F83FFFC47C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{243CB12F-B386-462C-9A4E-0D113E2FE932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1920" windowWidth="9936" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
   <si>
     <t>ID</t>
   </si>
@@ -32,6 +32,42 @@
   </si>
   <si>
     <t>Department</t>
+  </si>
+  <si>
+    <t>gopi</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>charan</t>
+  </si>
+  <si>
+    <t>RPC</t>
+  </si>
+  <si>
+    <t>niteesh</t>
+  </si>
+  <si>
+    <t>operator</t>
+  </si>
+  <si>
+    <t>Inv</t>
+  </si>
+  <si>
+    <t>prasad</t>
+  </si>
+  <si>
+    <t>achibabu</t>
+  </si>
+  <si>
+    <t>coordinator</t>
+  </si>
+  <si>
+    <t>Inbound</t>
   </si>
 </sst>
 </file>
@@ -383,7 +419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -404,6 +440,76 @@
         <v>3</v>
       </c>
     </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>13161</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>13655</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>13654</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>13653</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>13652</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
